--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.81307230256254</v>
+        <v>1.919624249166413</v>
       </c>
       <c r="D2" t="n">
-        <v>10.42050447820291</v>
+        <v>1.693331977707973</v>
       </c>
       <c r="E2" t="n">
-        <v>18.23016659907789</v>
+        <v>2.962402072350157</v>
       </c>
       <c r="F2" t="n">
-        <v>15.00847142198692</v>
+        <v>2.438876606072874</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91725384661009</v>
+        <v>7.461553750074141</v>
       </c>
       <c r="D3" t="n">
-        <v>32.3264823049124</v>
+        <v>5.253053374548266</v>
       </c>
       <c r="E3" t="n">
-        <v>18.23016659907789</v>
+        <v>2.962402072350157</v>
       </c>
       <c r="F3" t="n">
-        <v>15.00847142198692</v>
+        <v>2.438876606072874</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.39841892832686</v>
+        <v>7.539743075853115</v>
       </c>
       <c r="D4" t="n">
-        <v>51.20338135847459</v>
+        <v>8.320549470752121</v>
       </c>
       <c r="E4" t="n">
-        <v>18.23016659907789</v>
+        <v>2.962402072350157</v>
       </c>
       <c r="F4" t="n">
-        <v>15.00847142198692</v>
+        <v>2.438876606072874</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.805680522164479</v>
+        <v>1.268423084851728</v>
       </c>
       <c r="D5" t="n">
-        <v>21.80426327506455</v>
+        <v>3.54319278219799</v>
       </c>
       <c r="E5" t="n">
-        <v>18.23016659907789</v>
+        <v>2.962402072350157</v>
       </c>
       <c r="F5" t="n">
-        <v>15.00847142198692</v>
+        <v>2.438876606072874</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
